--- a/general_cards.xlsx
+++ b/general_cards.xlsx
@@ -193,29 +193,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.000000"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -238,17 +221,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,211 +723,211 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="45">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" ht="45">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="135">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" ht="75">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" ht="60">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="135">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" ht="105">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" ht="135">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" ht="60">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" ht="120">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" ht="120">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" ht="90">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" ht="75">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="15" ht="75">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" ht="75">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" ht="105">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" ht="90">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="19" ht="105">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" t="s">
         <v>56</v>
       </c>
     </row>

--- a/general_cards.xlsx
+++ b/general_cards.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>IMAGE</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Hack</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 2 Damage.</t>
+    <t xml:space="preserve">Deal 4 Damage to the Monster.</t>
   </si>
   <si>
     <t>cardimages/search.png</t>
@@ -51,16 +51,16 @@
     <t>Commit</t>
   </si>
   <si>
-    <t xml:space="preserve">Discard 3, then draw up to max hand size. Skip next turn.</t>
+    <t xml:space="preserve">Discard 3 and then draw up to your max hand size. Skip your next turn.</t>
   </si>
   <si>
     <t>cardimages/burn_it.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Burn It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exhaust X cards from hand. Draw X.</t>
+    <t xml:space="preserve">Burn it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhaust X cards from your hand. Draw X cards.</t>
   </si>
   <si>
     <t>cardimages/hunker_down.png</t>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Hunker Down</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevent 3. Exhaust.</t>
+    <t xml:space="preserve">Prevent 6 Damage you would take this turn. Exhaust.</t>
   </si>
   <si>
     <t>cardimages/play_dead.png</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Play Dead</t>
   </si>
   <si>
-    <t xml:space="preserve">Skip next turn. Prevent 1 this turn &amp; 3 next turn. Draw 1.</t>
+    <t xml:space="preserve">Skip your next turn. Prevent 2 Damage this turn and 6 Damage next turn. Draw 1.</t>
   </si>
   <si>
     <t>cardimages/boot_knife.png</t>
@@ -87,16 +87,16 @@
     <t xml:space="preserve">Boot Knife</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1. If discarded: deal 1 &amp; place on top of deck.</t>
+    <t xml:space="preserve">Deal 2 Damage. If this card is discarded, deal 2 Damage to the Monster and place this on top of your deck.</t>
   </si>
   <si>
     <t>cardimages/torch_it.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Torch It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deal 1 this turn; stays in play, deals 1 next turn, then discard.</t>
+    <t xml:space="preserve">Torch It!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 2 Damage this turn. Leave this card in front of you; it deals 2 Damage again next turn, then discard.</t>
   </si>
   <si>
     <t>cardimages/treasure_trove.png</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Open Book</t>
   </si>
   <si>
-    <t xml:space="preserve">Reveal hand; left player discards any number; draw X+1.</t>
+    <t xml:space="preserve">The Adventurer to your left discards any number of cards from your hand. Then draw X+1, where X is the number discarded.</t>
   </si>
   <si>
     <t>cardimages/gamble.png</t>
@@ -123,7 +123,7 @@
     <t>Gamble</t>
   </si>
   <si>
-    <t xml:space="preserve">Roll die: odd → Draw 2 &amp; Gather 2; even → Discard 1.</t>
+    <t xml:space="preserve">Roll a die: if odd, Draw 2 and Gather 2; if even, Discard 1.</t>
   </si>
   <si>
     <t>cardimages/opportunity.png</t>
@@ -141,13 +141,13 @@
     <t>Expectation</t>
   </si>
   <si>
-    <t xml:space="preserve">Change the order of monster cards.</t>
+    <t xml:space="preserve">Change the order of the monster cards.</t>
   </si>
   <si>
     <t>cardimages/be_gone.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Be Gone</t>
+    <t xml:space="preserve">Be gone!</t>
   </si>
   <si>
     <t xml:space="preserve">Exile a card from your hand.</t>
@@ -162,13 +162,31 @@
     <t xml:space="preserve">Avoid the monster card this turn.</t>
   </si>
   <si>
+    <t>cardimages/predict.png</t>
+  </si>
+  <si>
+    <t>Predict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scry 3, draw 2.</t>
+  </si>
+  <si>
+    <t>cardimages/awareness.png</t>
+  </si>
+  <si>
+    <t>Awareness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose one: Scry 2, Gather 1, or Draw 1.</t>
+  </si>
+  <si>
     <t>cardimages/beg.png</t>
   </si>
   <si>
     <t>Beg</t>
   </si>
   <si>
-    <t xml:space="preserve">Name a resource; each adventurer gives you one if able.</t>
+    <t xml:space="preserve">Name a resource type; each other adventurer must give you a token of that type if able.</t>
   </si>
   <si>
     <t>cardimages/monster_disguise.png</t>
@@ -177,16 +195,16 @@
     <t xml:space="preserve">Monster Disguise</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 to all adventurers except yourself.</t>
+    <t xml:space="preserve">Deal 2 Damage to all adventurers except yourself.</t>
   </si>
   <si>
     <t>cardimages/all_for_one.png</t>
   </si>
   <si>
-    <t xml:space="preserve">All for One</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deal 5, Prevent 5, exile. If discarded: Gather 1.</t>
+    <t xml:space="preserve">All for One/One for All</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 10 Damage to the Monster, Prevent 10 Damage, then exile this card. If this card is discarded, Gather 1.</t>
   </si>
 </sst>
 </file>
@@ -721,6 +739,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" width="35.28125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="19.28125"/>
+    <col bestFit="1" min="3" max="3" width="126.7109375"/>
+  </cols>
   <sheetData>
     <row r="1" ht="15">
       <c r="A1" t="s">
@@ -929,6 +952,28 @@
       </c>
       <c r="C19" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -951,6 +996,8 @@
     <hyperlink r:id="rId16" ref="B17" tooltip=""/>
     <hyperlink r:id="rId17" ref="B18" tooltip=""/>
     <hyperlink r:id="rId18" ref="B19" tooltip=""/>
+    <hyperlink r:id="rId19" ref="B20" tooltip=""/>
+    <hyperlink r:id="rId20" ref="B21" tooltip=""/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/general_cards.xlsx
+++ b/general_cards.xlsx
@@ -54,10 +54,10 @@
     <t xml:space="preserve">Discard 3 and then draw up to your max hand size. Skip your next turn.</t>
   </si>
   <si>
-    <t>cardimages/burn_it.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burn it</t>
+    <t>cardimages/refresh.png</t>
+  </si>
+  <si>
+    <t>Refresh</t>
   </si>
   <si>
     <t xml:space="preserve">Exhaust X cards from your hand. Draw X cards.</t>
@@ -201,7 +201,7 @@
     <t>cardimages/all_for_one.png</t>
   </si>
   <si>
-    <t xml:space="preserve">All for One/One for All</t>
+    <t xml:space="preserve">All for One</t>
   </si>
   <si>
     <t xml:space="preserve">Deal 10 Damage to the Monster, Prevent 10 Damage, then exile this card. If this card is discarded, Gather 1.</t>
@@ -741,7 +741,7 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="1" max="1" width="35.28125"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="19.28125"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" width="19.80078125"/>
     <col bestFit="1" min="3" max="3" width="126.7109375"/>
   </cols>
   <sheetData>

--- a/general_cards.xlsx
+++ b/general_cards.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t>IMAGE</t>
   </si>
@@ -205,6 +205,36 @@
   </si>
   <si>
     <t xml:space="preserve">Deal 10 Damage to the Monster, Prevent 10 Damage, then exile this card. If this card is discarded, Gather 1.</t>
+  </si>
+  <si>
+    <t>cardimages/grand_show.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Show</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reveal the top 5 cards of your deck, put any cards that don't deal damage into your hand.</t>
+  </si>
+  <si>
+    <t>cardimages/deep_pockets.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deep Pockets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 1 Damage for each type of resource you have in your backpack.</t>
+  </si>
+  <si>
+    <t>cardimages/exhausting_speech.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Double Talk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each other adventurer must exhaust a card from their hand or Take 1 Damage. Gather 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -976,6 +1006,44 @@
         <v>62</v>
       </c>
     </row>
+    <row r="22" ht="14.25">
+      <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25">
+      <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25">
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2" tooltip=""/>
